--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260810.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>712,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>261,000</t>
+          <t>712,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
